--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N32_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.34151396215869</v>
+        <v>9.102818680520157</v>
       </c>
       <c r="D2" t="n">
-        <v>15.19822491429602</v>
+        <v>8.552218895175978</v>
       </c>
       <c r="E2" t="n">
-        <v>6.800679441981468</v>
+        <v>6.245097399571807</v>
       </c>
       <c r="F2" t="n">
-        <v>4.893811748977079</v>
+        <v>4.407040590727876</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.00073585482149</v>
+        <v>17.34151396215869</v>
       </c>
       <c r="D3" t="n">
-        <v>8.258008815430994</v>
+        <v>15.19822491429602</v>
       </c>
       <c r="E3" t="n">
-        <v>6.800679441981468</v>
+        <v>6.245097399571807</v>
       </c>
       <c r="F3" t="n">
-        <v>4.893811748977079</v>
+        <v>4.407040590727876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.07144235478947</v>
+        <v>18.00073585482149</v>
       </c>
       <c r="D4" t="n">
-        <v>13.29289770746377</v>
+        <v>8.258008815430994</v>
       </c>
       <c r="E4" t="n">
-        <v>6.800679441981468</v>
+        <v>6.245097399571807</v>
       </c>
       <c r="F4" t="n">
-        <v>4.893811748977079</v>
+        <v>4.407040590727876</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,23 +576,55 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>14.07144235478947</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.29289770746377</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.245097399571807</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.407040590727876</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N32.png</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
         <v>1.146253272562745</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>2.583141656709175</v>
       </c>
-      <c r="E5" t="n">
-        <v>6.800679441981468</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.893811748977079</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>6.245097399571807</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.407040590727876</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.102818680520157</v>
+        <v>1.479208035584526</v>
       </c>
       <c r="D2" t="n">
-        <v>8.552218895175978</v>
+        <v>1.389735570466097</v>
       </c>
       <c r="E2" t="n">
-        <v>6.245097399571807</v>
+        <v>1.014828327430419</v>
       </c>
       <c r="F2" t="n">
-        <v>4.407040590727876</v>
+        <v>0.71614409599328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.34151396215869</v>
+        <v>2.817996018850787</v>
       </c>
       <c r="D3" t="n">
-        <v>15.19822491429602</v>
+        <v>2.469711548573103</v>
       </c>
       <c r="E3" t="n">
-        <v>6.245097399571807</v>
+        <v>1.014828327430419</v>
       </c>
       <c r="F3" t="n">
-        <v>4.407040590727876</v>
+        <v>0.71614409599328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.00073585482149</v>
+        <v>2.925119576408492</v>
       </c>
       <c r="D4" t="n">
-        <v>8.258008815430994</v>
+        <v>1.341926432507537</v>
       </c>
       <c r="E4" t="n">
-        <v>6.245097399571807</v>
+        <v>1.014828327430419</v>
       </c>
       <c r="F4" t="n">
-        <v>4.407040590727876</v>
+        <v>0.71614409599328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.07144235478947</v>
+        <v>2.286609382653289</v>
       </c>
       <c r="D5" t="n">
-        <v>13.29289770746377</v>
+        <v>2.160095877462863</v>
       </c>
       <c r="E5" t="n">
-        <v>6.245097399571807</v>
+        <v>1.014828327430419</v>
       </c>
       <c r="F5" t="n">
-        <v>4.407040590727876</v>
+        <v>0.71614409599328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.146253272562745</v>
+        <v>0.1862661567914461</v>
       </c>
       <c r="D6" t="n">
-        <v>2.583141656709175</v>
+        <v>0.4197605192152409</v>
       </c>
       <c r="E6" t="n">
-        <v>6.245097399571807</v>
+        <v>1.014828327430419</v>
       </c>
       <c r="F6" t="n">
-        <v>4.407040590727876</v>
+        <v>0.71614409599328</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
